--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$836</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$838</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16249,53 +16249,43 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DO-009482014/2025</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DO-009482046/2025</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="D832" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -16305,51 +16295,85 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>-19.747173</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>-50.219328</t>
+          <t>-43.9495793253305</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
           <t>DC-9493529/2026</t>
         </is>
       </c>
-      <c r="B836" t="inlineStr">
+      <c r="B838" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D836"/>
+  <autoFilter ref="A1:D838"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$838</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$843</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16215,29 +16215,19 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9493205/2026</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>-19.7469167</t>
-        </is>
-      </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>-47.9483714</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>D0-009482032/2025</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -16249,7 +16239,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DO-009482014/2025</t>
+          <t>DO-9481987/2025</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -16261,7 +16251,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>DO-009482055/2025</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -16273,41 +16263,41 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>-19.7469167</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>-47.9483714</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DO-009482014/2025</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -16319,61 +16309,131 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DO-009482046/2025</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DO-009482017/2025</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="D837" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
+          <t>DC-9496643/2026</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>DC-9496643/2026</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>DC-9498666/2026</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
           <t>DC-9493529/2026</t>
         </is>
       </c>
-      <c r="B838" t="inlineStr">
+      <c r="B843" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D838"/>
+  <autoFilter ref="A1:D843"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$843</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$854</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16379,61 +16379,233 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C841" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-17.335013</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-44.943418</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
           <t>DC-9493529/2026</t>
         </is>
       </c>
-      <c r="B843" t="inlineStr">
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D843"/>
+  <autoFilter ref="A1:D854"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$854</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$858</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16215,48 +16215,88 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>DO-9493205/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>D0-009482032/2025</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DO-9481987/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DO-009482055/2025</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
@@ -16297,36 +16337,66 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DO-009482014/2025</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>DO-009482017/2025</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
@@ -16481,29 +16551,19 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="C847" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -16513,41 +16573,41 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-44.5829004</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.8541147</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -16559,53 +16619,131 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
           <t>DM-016/2024-A</t>
         </is>
       </c>
-      <c r="B854" t="inlineStr">
+      <c r="B858" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D854"/>
+  <autoFilter ref="A1:D858"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$858</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$861</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16403,12 +16403,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
@@ -16420,36 +16420,36 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
+          <t>Obra 2</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -16461,41 +16461,41 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C842" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -16507,85 +16507,75 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C845" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-50.219328</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
           <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C848" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -16595,53 +16585,63 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-44.5829004</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
+          <t>-46.3795013</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -16651,77 +16651,97 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-43.983052</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
+          <t>Obra 1</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
           <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -16733,17 +16753,53 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
           <t>DM-016/2024-A</t>
         </is>
       </c>
-      <c r="B858" t="inlineStr">
+      <c r="B861" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D858"/>
+  <autoFilter ref="A1:D861"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F869"/>
+  <dimension ref="A1:F893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25351,36 +25351,36 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D842" t="inlineStr"/>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -25388,31 +25388,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -25424,19 +25416,19 @@
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25448,19 +25440,19 @@
       <c r="E845" t="inlineStr"/>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25468,31 +25460,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25504,19 +25488,19 @@
       <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25528,19 +25512,19 @@
       <c r="E848" t="inlineStr"/>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25548,63 +25532,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
       <c r="F849" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -25616,19 +25584,19 @@
       <c r="E851" t="inlineStr"/>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25636,31 +25604,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25668,63 +25628,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E854" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25734,29 +25678,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-43.9495793253305</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25768,19 +25712,19 @@
       <c r="E856" t="inlineStr"/>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25792,19 +25736,19 @@
       <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25812,23 +25756,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25840,51 +25792,43 @@
       <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25894,61 +25838,61 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-50.219328</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -25960,19 +25904,19 @@
       <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25980,23 +25924,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -26004,23 +25956,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr"/>
-      <c r="E865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26028,23 +25988,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
-      <c r="E866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26052,23 +26020,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26076,49 +26052,649 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E868" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2301520 000036/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>9422079</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>9424304</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
           <t>DM-022/2024-A</t>
         </is>
       </c>
-      <c r="B869" t="inlineStr">
+      <c r="B893" t="inlineStr">
         <is>
           <t>9427765</t>
         </is>
       </c>
-      <c r="C869" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr">
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
         <is>
           <t>-20.6829764</t>
         </is>
       </c>
-      <c r="E869" t="inlineStr">
+      <c r="E893" t="inlineStr">
         <is>
           <t>-44.8232506</t>
         </is>
       </c>
-      <c r="F869" t="inlineStr">
+      <c r="F893" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F893"/>
+  <dimension ref="A1:F868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23138,11 +23138,7 @@
           <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>9469794</t>
-        </is>
-      </c>
+      <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23150,11 +23146,7 @@
       </c>
       <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
-      <c r="F765" t="inlineStr">
-        <is>
-          <t>2301931 000002/2025</t>
-        </is>
-      </c>
+      <c r="F765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -24010,11 +24002,7 @@
           <t xml:space="preserve">DC-9441355/2024 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>9441355</t>
-        </is>
-      </c>
+      <c r="B795" t="inlineStr"/>
       <c r="C795" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -24030,11 +24018,7 @@
           <t>-41.506751</t>
         </is>
       </c>
-      <c r="F795" t="inlineStr">
-        <is>
-          <t>2301520 000014/2024</t>
-        </is>
-      </c>
+      <c r="F795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -25159,76 +25143,44 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr"/>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E835" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
-        </is>
-      </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>9482046</t>
-        </is>
-      </c>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr"/>
       <c r="C836" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E836" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -25255,12 +25207,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -25268,23 +25220,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D838" t="inlineStr"/>
-      <c r="E838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -25292,11 +25252,19 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D839" t="inlineStr"/>
-      <c r="E839" t="inlineStr"/>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
@@ -25351,60 +25319,60 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-21.1994491</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-43.7852868</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -25412,23 +25380,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr"/>
-      <c r="E844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25440,19 +25416,19 @@
       <c r="E845" t="inlineStr"/>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25464,19 +25440,19 @@
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25484,23 +25460,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
-      <c r="E847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25512,19 +25496,19 @@
       <c r="E848" t="inlineStr"/>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25536,19 +25520,19 @@
       <c r="E849" t="inlineStr"/>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25556,47 +25540,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
-      <c r="E850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25608,19 +25608,19 @@
       <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25628,47 +25628,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr"/>
-      <c r="E853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D854" t="inlineStr"/>
-      <c r="E854" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25678,29 +25694,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25708,23 +25724,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25736,19 +25760,19 @@
       <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25756,55 +25780,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E858" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25812,87 +25836,87 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>-19.747173</t>
+          <t>-16.12119845072</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>-50.219328</t>
+          <t>-45.6488268407393</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -25904,19 +25928,19 @@
       <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25924,31 +25948,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E864" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr"/>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -25956,31 +25972,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E865" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -25988,31 +25996,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26022,29 +26022,29 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.8518635</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-41.5076927</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26052,649 +26052,17 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
       <c r="F868" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C869" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B870" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C870" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B871" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C871" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B872" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C872" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr"/>
-      <c r="E872" t="inlineStr"/>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="873">
-      <c r="A873" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B873" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C873" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
-      <c r="F873" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="874">
-      <c r="A874" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B874" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C874" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D874" t="inlineStr"/>
-      <c r="E874" t="inlineStr"/>
-      <c r="F874" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="875">
-      <c r="A875" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B875" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C875" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D875" t="inlineStr"/>
-      <c r="E875" t="inlineStr"/>
-      <c r="F875" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C876" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D876" t="inlineStr"/>
-      <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr"/>
-      <c r="E877" t="inlineStr"/>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr"/>
-      <c r="E878" t="inlineStr"/>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C880" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr"/>
-      <c r="E882" t="inlineStr"/>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B883" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C883" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D883" t="inlineStr"/>
-      <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B884" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E884" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
-      <c r="F884" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B885" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C885" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E885" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
-      <c r="F885" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B886" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C886" t="inlineStr">
-        <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E886" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
-      <c r="F886" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="887">
-      <c r="A887" t="inlineStr">
-        <is>
-          <t>DC-9493529/2026</t>
-        </is>
-      </c>
-      <c r="B887" t="inlineStr">
-        <is>
-          <t>9493529</t>
-        </is>
-      </c>
-      <c r="C887" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D887" t="inlineStr"/>
-      <c r="E887" t="inlineStr"/>
-      <c r="F887" t="inlineStr">
-        <is>
-          <t>2301520 000036/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="888">
-      <c r="A888" t="inlineStr">
-        <is>
-          <t>DM-012/2024-A</t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr">
-        <is>
-          <t>9422079</t>
-        </is>
-      </c>
-      <c r="C888" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
-      <c r="F888" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t>DM-9502116/2026</t>
-        </is>
-      </c>
-      <c r="B889" t="inlineStr">
-        <is>
-          <t>9502116</t>
-        </is>
-      </c>
-      <c r="C889" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr">
-        <is>
-          <t>2301762 000026/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr">
-        <is>
-          <t>DM-018/2024-A</t>
-        </is>
-      </c>
-      <c r="B890" t="inlineStr">
-        <is>
-          <t>9424304</t>
-        </is>
-      </c>
-      <c r="C890" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D890" t="inlineStr"/>
-      <c r="E890" t="inlineStr"/>
-      <c r="F890" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" t="inlineStr">
-        <is>
-          <t>DM-016/2024-A</t>
-        </is>
-      </c>
-      <c r="B891" t="inlineStr">
-        <is>
-          <t>9424337</t>
-        </is>
-      </c>
-      <c r="C891" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D891" t="inlineStr"/>
-      <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" t="inlineStr">
-        <is>
-          <t>DM-020/2024-A</t>
-        </is>
-      </c>
-      <c r="B892" t="inlineStr">
-        <is>
-          <t>9427674</t>
-        </is>
-      </c>
-      <c r="C892" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E892" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
-      <c r="F892" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="893">
-      <c r="A893" t="inlineStr">
-        <is>
-          <t>DM-022/2024-A</t>
-        </is>
-      </c>
-      <c r="B893" t="inlineStr">
-        <is>
-          <t>9427765</t>
-        </is>
-      </c>
-      <c r="C893" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E893" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
-      <c r="F893" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F868"/>
+  <dimension ref="A1:F872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25319,62 +25319,58 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C842" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>-21.1994491</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
-      <c r="F842" t="inlineStr"/>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
-        </is>
-      </c>
-      <c r="B844" t="inlineStr">
-        <is>
-          <t>9496643</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25382,53 +25378,49 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>1301606 000002/2025</t>
-        </is>
-      </c>
+          <t>-43.7852868</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D845" t="inlineStr"/>
       <c r="E845" t="inlineStr"/>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25436,23 +25428,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr"/>
-      <c r="E846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25460,31 +25460,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25503,12 +25495,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25516,8 +25508,16 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
-      <c r="E849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F849" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
@@ -25527,12 +25527,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25540,63 +25540,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
       <c r="F850" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E851" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25604,55 +25588,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
-      <c r="E852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25660,31 +25652,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E854" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25694,29 +25678,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25726,29 +25710,29 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25756,23 +25740,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25780,55 +25772,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25836,63 +25828,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D861" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E861" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25904,43 +25880,51 @@
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25948,47 +25932,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D865" t="inlineStr"/>
-      <c r="E865" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26000,19 +26000,19 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26020,49 +26020,145 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9424304</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
           <t>DM-022/2024-A</t>
         </is>
       </c>
-      <c r="B868" t="inlineStr">
+      <c r="B872" t="inlineStr">
         <is>
           <t>9427765</t>
         </is>
       </c>
-      <c r="C868" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D868" t="inlineStr">
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
         <is>
           <t>-20.6829764</t>
         </is>
       </c>
-      <c r="E868" t="inlineStr">
+      <c r="E872" t="inlineStr">
         <is>
           <t>-44.8232506</t>
         </is>
       </c>
-      <c r="F868" t="inlineStr">
+      <c r="F872" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F872"/>
+  <dimension ref="A1:F868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25319,58 +25319,62 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-21.1994491</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-43.7852868</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
-        </is>
-      </c>
-      <c r="B844" t="inlineStr"/>
+          <t>DC-9496643/2026</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>9496643</t>
+        </is>
+      </c>
       <c r="C844" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25378,49 +25382,53 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr"/>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>1301606 000002/2025</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D845" t="inlineStr"/>
       <c r="E845" t="inlineStr"/>
       <c r="F845" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25428,31 +25436,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25460,23 +25460,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
-      <c r="E847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25495,12 +25503,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25508,16 +25516,8 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
       <c r="F849" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
@@ -25527,12 +25527,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25540,47 +25540,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
-      <c r="E850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25588,63 +25604,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25652,23 +25660,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr"/>
-      <c r="E854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25678,29 +25694,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25710,29 +25726,29 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25740,31 +25756,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E857" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25772,55 +25780,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E858" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25828,47 +25836,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D861" t="inlineStr"/>
-      <c r="E861" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25880,51 +25904,43 @@
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D863" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E863" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25932,63 +25948,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E864" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr"/>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D865" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E865" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26000,19 +26000,19 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26020,23 +26020,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26044,121 +26052,17 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
       <c r="F868" t="inlineStr">
-        <is>
-          <t>2301762 000026/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>DM-018/2024-A</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr">
-        <is>
-          <t>9424304</t>
-        </is>
-      </c>
-      <c r="C869" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>DM-016/2024-A</t>
-        </is>
-      </c>
-      <c r="B870" t="inlineStr">
-        <is>
-          <t>9424337</t>
-        </is>
-      </c>
-      <c r="C870" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>DM-020/2024-A</t>
-        </is>
-      </c>
-      <c r="B871" t="inlineStr">
-        <is>
-          <t>9427674</t>
-        </is>
-      </c>
-      <c r="C871" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" t="inlineStr">
-        <is>
-          <t>DM-022/2024-A</t>
-        </is>
-      </c>
-      <c r="B872" t="inlineStr">
-        <is>
-          <t>9427765</t>
-        </is>
-      </c>
-      <c r="C872" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E872" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F871"/>
+  <dimension ref="A1:F879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25562,7 +25562,11 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B850" t="inlineStr"/>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C850" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -25586,7 +25590,11 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B851" t="inlineStr"/>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -25594,12 +25602,12 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -25610,20 +25618,24 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B852" t="inlineStr"/>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -25634,20 +25646,24 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B853" t="inlineStr"/>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F853" t="inlineStr"/>
@@ -25655,12 +25671,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25670,29 +25686,25 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25702,29 +25714,25 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25734,29 +25742,25 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F856" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25766,29 +25770,25 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F857" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25815,12 +25815,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25828,23 +25828,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25852,23 +25860,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25876,23 +25892,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr"/>
-      <c r="E861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25902,27 +25926,31 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>-19.7469167</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>-47.9483714</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B863" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C863" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25930,7 +25958,11 @@
       </c>
       <c r="D863" t="inlineStr"/>
       <c r="E863" t="inlineStr"/>
-      <c r="F863" t="inlineStr"/>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -25983,12 +26015,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -25996,31 +26028,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26028,31 +26052,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26062,12 +26078,12 @@
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-19.7469167</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>-44.943418</t>
+          <t>-47.9483714</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
@@ -26079,14 +26095,10 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr"/>
       <c r="C869" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26094,21 +26106,17 @@
       </c>
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+      <c r="F869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26120,19 +26128,19 @@
       <c r="E870" t="inlineStr"/>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26143,6 +26151,222 @@
       <c r="D871" t="inlineStr"/>
       <c r="E871" t="inlineStr"/>
       <c r="F871" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25582,7 +25582,11 @@
           <t>-46.62095644999281</t>
         </is>
       </c>
-      <c r="F850" t="inlineStr"/>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -25610,7 +25614,11 @@
           <t>-46.62095644999281</t>
         </is>
       </c>
-      <c r="F851" t="inlineStr"/>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -25638,7 +25646,11 @@
           <t>-46.58862620066699</t>
         </is>
       </c>
-      <c r="F852" t="inlineStr"/>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -25666,7 +25678,11 @@
           <t>-46.58862620066699</t>
         </is>
       </c>
-      <c r="F853" t="inlineStr"/>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -25694,7 +25710,11 @@
           <t>-46.687872082284</t>
         </is>
       </c>
-      <c r="F854" t="inlineStr"/>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -25722,7 +25742,11 @@
           <t>-46.687872082284</t>
         </is>
       </c>
-      <c r="F855" t="inlineStr"/>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -25750,7 +25774,11 @@
           <t>-46.62095644999281</t>
         </is>
       </c>
-      <c r="F856" t="inlineStr"/>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -25778,7 +25806,11 @@
           <t>-46.62095644999281</t>
         </is>
       </c>
-      <c r="F857" t="inlineStr"/>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -25991,12 +26023,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -26008,19 +26040,19 @@
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26028,25 +26060,29 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
-      <c r="E866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>-19.7469167</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-47.9483714</t>
+        </is>
+      </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr">
-        <is>
-          <t>9497685</t>
-        </is>
-      </c>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26054,51 +26090,35 @@
       </c>
       <c r="D867" t="inlineStr"/>
       <c r="E867" t="inlineStr"/>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>2301762 000023/2025</t>
-        </is>
-      </c>
+      <c r="F867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
-        </is>
-      </c>
-      <c r="B868" t="inlineStr">
-        <is>
-          <t>9414460</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr"/>
       <c r="C868" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>-19.7469167</t>
-        </is>
-      </c>
-      <c r="E868" t="inlineStr">
-        <is>
-          <t>-47.9483714</t>
-        </is>
-      </c>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C869" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26106,7 +26126,11 @@
       </c>
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -26135,12 +26159,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26148,23 +26172,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26172,23 +26204,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr"/>
-      <c r="E872" t="inlineStr"/>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26196,23 +26236,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26220,31 +26268,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E874" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26252,31 +26292,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E875" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -26284,89 +26316,9 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E876" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr"/>
-      <c r="E877" t="inlineStr"/>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr"/>
-      <c r="E878" t="inlineStr"/>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>DM-008/2024-A</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>9422064</t>
-        </is>
-      </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F882"/>
+  <dimension ref="A1:F876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25190,12 +25190,12 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -25217,17 +25217,17 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25249,17 +25249,17 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25271,12 +25271,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -25286,29 +25286,29 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -25318,29 +25318,29 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -25350,29 +25350,29 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -25380,31 +25380,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>-17.10715545158923</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>-46.62095644999281</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -25414,61 +25406,53 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25478,29 +25462,29 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-43.9495793253305</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25512,19 +25496,19 @@
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25536,19 +25520,19 @@
       <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25558,12 +25542,12 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-17.335013</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
+          <t>-44.943418</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -25575,36 +25559,36 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D849" t="inlineStr"/>
       <c r="E849" t="inlineStr"/>
       <c r="F849" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25612,33 +25596,21 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
       <c r="F850" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
-        </is>
-      </c>
-      <c r="B851" t="inlineStr">
-        <is>
-          <t>9453556</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr"/>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25646,21 +25618,17 @@
       </c>
       <c r="D851" t="inlineStr"/>
       <c r="E851" t="inlineStr"/>
-      <c r="F851" t="inlineStr">
-        <is>
-          <t>2301520 000041/2025</t>
-        </is>
-      </c>
+      <c r="F851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25672,19 +25640,19 @@
       <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25694,29 +25662,29 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-44.943418</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25724,23 +25692,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr"/>
-      <c r="E854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25752,35 +25728,51 @@
       <c r="E855" t="inlineStr"/>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B856" t="inlineStr"/>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>9275590</t>
+        </is>
+      </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
-      <c r="F856" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2301901 000003/2021</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25792,17 +25784,21 @@
       <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B858" t="inlineStr"/>
+          <t>DM-014/2024-A</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>9424302</t>
+        </is>
+      </c>
       <c r="C858" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25810,25 +25806,29 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
-      <c r="F858" t="inlineStr"/>
+          <t>-44.5829004</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25838,77 +25838,93 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>-19.747173</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>-50.219328</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B860" t="inlineStr"/>
+          <t>DC-9505062/2026</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>9505062</t>
+        </is>
+      </c>
       <c r="C860" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
-      <c r="F860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>2301520 000044/2025</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25920,51 +25936,51 @@
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-16.11741660736296</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-45.71048533230583</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25974,61 +25990,61 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-16.11921421383736</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-45.58712745575681</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-16.12119845072</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-45.6488268407393</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26036,31 +26052,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26072,19 +26080,19 @@
       <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26096,51 +26104,43 @@
       <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E869" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26148,63 +26148,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E870" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-17.8518635</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-41.5076927</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26212,47 +26204,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr"/>
-      <c r="E872" t="inlineStr"/>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26264,185 +26264,57 @@
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D875" t="inlineStr"/>
       <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>DM-020/2024-A</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>9427674</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>DM-022/2024-A</t>
-        </is>
-      </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t>9427765</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr"/>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>Obra 4</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr"/>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr"/>
-      <c r="C880" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
-      <c r="F880" t="inlineStr"/>
-    </row>
-    <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr"/>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
-    </row>
-    <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr"/>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr"/>
-      <c r="E882" t="inlineStr"/>
-      <c r="F882" t="inlineStr"/>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F876"/>
+  <dimension ref="A1:F880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25271,44 +25271,28 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr"/>
       <c r="C839" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+      <c r="D839" t="inlineStr"/>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -25335,12 +25319,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -25367,12 +25351,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -25380,23 +25364,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -25404,111 +25396,119 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>-21.1994491</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr">
-        <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr"/>
-      <c r="E844" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>-21.1994491</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>-43.7852868</t>
+        </is>
+      </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
+          <t>-42.91331545001727</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D846" t="inlineStr"/>
-      <c r="E846" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>-21.23264738347681</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25516,55 +25516,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
-      <c r="E847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-21.23528484003703</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25572,23 +25572,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
-      <c r="E849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25600,17 +25608,21 @@
       <c r="E850" t="inlineStr"/>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B851" t="inlineStr"/>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25618,17 +25630,21 @@
       </c>
       <c r="D851" t="inlineStr"/>
       <c r="E851" t="inlineStr"/>
-      <c r="F851" t="inlineStr"/>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25636,23 +25652,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
-      <c r="E852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25660,31 +25684,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25692,33 +25708,21 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E854" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
       <c r="F854" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B855" t="inlineStr">
-        <is>
-          <t>9512044</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr"/>
       <c r="C855" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25726,53 +25730,41 @@
       </c>
       <c r="D855" t="inlineStr"/>
       <c r="E855" t="inlineStr"/>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>2301762 000001/2026</t>
-        </is>
-      </c>
+      <c r="F855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25780,23 +25772,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25806,29 +25806,29 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-50.219328</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25836,63 +25836,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25900,31 +25892,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E861" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25932,55 +25916,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25990,61 +25982,61 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26056,43 +26048,51 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26100,47 +26100,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26152,19 +26168,19 @@
       <c r="E870" t="inlineStr"/>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26172,31 +26188,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26204,55 +26212,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E872" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26264,53 +26264,165 @@
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D875" t="inlineStr"/>
-      <c r="E875" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B876" t="inlineStr">
+      <c r="B877" t="inlineStr">
         <is>
           <t>9511902</t>
         </is>
       </c>
-      <c r="C876" t="inlineStr">
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
         <is>
           <t>Obra 2</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr"/>
-      <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr">
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
         <is>
           <t>2301520 000001/2026</t>
         </is>
